--- a/data/HR_Audit_Report.xlsx
+++ b/data/HR_Audit_Report.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\honey\Documents\GitHub\hris-audit-dashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A853EC6F-7E4B-4D2C-A33F-B14F29642C1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D43939EE-3995-463E-961A-4243173ACE93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="21000" tabRatio="659" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19200" yWindow="0" windowWidth="19200" windowHeight="21000" tabRatio="659" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="6" r:id="rId1"/>
@@ -23,7 +23,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="15" r:id="rId8"/>
+    <pivotCache cacheId="0" r:id="rId8"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -348,8 +348,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
@@ -643,18 +644,22 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -667,14 +672,10 @@
     <xf numFmtId="0" fontId="9" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -684,15 +685,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -707,14 +699,27 @@
     <xf numFmtId="0" fontId="9" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3628,184 +3633,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AB1D9616-CFC8-48A1-9E09-D27FA24D9383}" name="PivotTable4" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
-  <location ref="A35:B65" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="6">
-    <pivotField axis="axisRow" showAll="0" sortType="ascending">
-      <items count="30">
-        <item x="15"/>
-        <item x="3"/>
-        <item x="17"/>
-        <item x="26"/>
-        <item x="18"/>
-        <item x="25"/>
-        <item x="8"/>
-        <item x="21"/>
-        <item x="16"/>
-        <item x="13"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="14"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="1"/>
-        <item x="24"/>
-        <item x="2"/>
-        <item x="19"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="7"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="28"/>
-        <item x="20"/>
-        <item x="5"/>
-        <item x="27"/>
-        <item x="6"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="30">
-    <i>
-      <x v="15"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="17"/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="28"/>
-    </i>
-    <i>
-      <x v="26"/>
-    </i>
-    <i>
-      <x v="21"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="19"/>
-    </i>
-    <i>
-      <x v="23"/>
-    </i>
-    <i>
-      <x v="22"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="20"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="18"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="25"/>
-    </i>
-    <i>
-      <x v="24"/>
-    </i>
-    <i>
-      <x v="16"/>
-    </i>
-    <i>
-      <x v="27"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of attendance_rate_pct" fld="5" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="3" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5C81D27C-4600-474B-846D-4F788ED126BB}" name="PivotTable1" cacheId="15" dataPosition="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="26">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5C81D27C-4600-474B-846D-4F788ED126BB}" name="PivotTable1" cacheId="0" dataPosition="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="26">
   <location ref="A1:B31" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="6">
     <pivotField axis="axisRow" showAll="0" sortType="ascending">
@@ -3971,6 +3799,183 @@
   </formats>
   <chartFormats count="1">
     <chartFormat chart="2" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AB1D9616-CFC8-48A1-9E09-D27FA24D9383}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+  <location ref="A35:B65" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="6">
+    <pivotField axis="axisRow" showAll="0" sortType="ascending">
+      <items count="30">
+        <item x="15"/>
+        <item x="3"/>
+        <item x="17"/>
+        <item x="26"/>
+        <item x="18"/>
+        <item x="25"/>
+        <item x="8"/>
+        <item x="21"/>
+        <item x="16"/>
+        <item x="13"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="14"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="1"/>
+        <item x="24"/>
+        <item x="2"/>
+        <item x="19"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="7"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="28"/>
+        <item x="20"/>
+        <item x="5"/>
+        <item x="27"/>
+        <item x="6"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="30">
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="28"/>
+    </i>
+    <i>
+      <x v="26"/>
+    </i>
+    <i>
+      <x v="21"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="19"/>
+    </i>
+    <i>
+      <x v="23"/>
+    </i>
+    <i>
+      <x v="22"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="25"/>
+    </i>
+    <i>
+      <x v="24"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="27"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of attendance_rate_pct" fld="5" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="3" format="1" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -4300,146 +4305,134 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:24" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
-      <c r="L2" s="11"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="11"/>
-      <c r="O2" s="11"/>
-      <c r="P2" s="11"/>
-      <c r="Q2" s="11"/>
-      <c r="R2" s="11"/>
-      <c r="S2" s="11"/>
-      <c r="T2" s="11"/>
-      <c r="U2" s="11"/>
-      <c r="V2" s="11"/>
-      <c r="W2" s="11"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="17"/>
+      <c r="Q2" s="17"/>
+      <c r="R2" s="17"/>
+      <c r="S2" s="17"/>
+      <c r="T2" s="17"/>
+      <c r="U2" s="17"/>
+      <c r="V2" s="17"/>
+      <c r="W2" s="17"/>
     </row>
     <row r="3" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
-      <c r="L3" s="12"/>
-      <c r="M3" s="12"/>
-      <c r="N3" s="12"/>
-      <c r="O3" s="12"/>
-      <c r="P3" s="12"/>
-      <c r="Q3" s="12"/>
-      <c r="R3" s="12"/>
-      <c r="S3" s="12"/>
-      <c r="T3" s="12"/>
-      <c r="U3" s="12"/>
-      <c r="V3" s="12"/>
-      <c r="W3" s="12"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="18"/>
+      <c r="L3" s="18"/>
+      <c r="M3" s="18"/>
+      <c r="N3" s="18"/>
+      <c r="O3" s="18"/>
+      <c r="P3" s="18"/>
+      <c r="Q3" s="18"/>
+      <c r="R3" s="18"/>
+      <c r="S3" s="18"/>
+      <c r="T3" s="18"/>
+      <c r="U3" s="18"/>
+      <c r="V3" s="18"/>
+      <c r="W3" s="18"/>
     </row>
     <row r="5" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B5" s="17">
+      <c r="B5" s="19">
         <f>COUNTA(Absenteeism!A2:A30)</f>
         <v>29</v>
       </c>
-      <c r="C5" s="18"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="23"/>
-      <c r="F5" s="17" t="str">
+      <c r="C5" s="20"/>
+      <c r="D5" s="21"/>
+      <c r="F5" s="19" t="str">
         <f>ROUND(AVERAGE(Absenteeism!F4:F32),1)&amp;"%"</f>
         <v>57.3%</v>
       </c>
-      <c r="G5" s="18"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="23"/>
-      <c r="J5" s="17">
+      <c r="G5" s="20"/>
+      <c r="H5" s="21"/>
+      <c r="J5" s="19">
         <f>SUM(Absenteeism!D4:D32)</f>
         <v>322</v>
       </c>
-      <c r="K5" s="18"/>
-      <c r="L5" s="19"/>
-      <c r="M5" s="23"/>
-      <c r="N5" s="17">
+      <c r="K5" s="20"/>
+      <c r="L5" s="21"/>
+      <c r="N5" s="19">
         <f>SUMIF('Punch Integrity'!A4:A9,"&lt;&gt;Clean", 'Punch Integrity'!B4:B9)-SUMIF('Punch Integrity'!A4:A9,"No data",'Punch Integrity'!B4:B9)</f>
         <v>231</v>
       </c>
-      <c r="O5" s="18"/>
-      <c r="P5" s="19"/>
-      <c r="Q5" s="23"/>
-      <c r="R5" s="31">
+      <c r="O5" s="20"/>
+      <c r="P5" s="21"/>
+      <c r="R5" s="28">
         <f>COUNTIF('HR Action Required'!F4:F32,"Critical - immediate review")</f>
         <v>7</v>
       </c>
-      <c r="S5" s="32"/>
-      <c r="T5" s="33"/>
-      <c r="V5" s="17" t="str">
+      <c r="S5" s="29"/>
+      <c r="T5" s="30"/>
+      <c r="V5" s="19" t="str">
         <f>ROUND(AVERAGE('Late Arrivals'!C4:C28),1)&amp;" mins"</f>
         <v>39.1 mins</v>
       </c>
-      <c r="W5" s="18"/>
-      <c r="X5" s="19"/>
+      <c r="W5" s="20"/>
+      <c r="X5" s="21"/>
     </row>
     <row r="6" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B6" s="20"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="23"/>
-      <c r="J6" s="20"/>
-      <c r="K6" s="21"/>
-      <c r="L6" s="22"/>
-      <c r="M6" s="23"/>
-      <c r="N6" s="20"/>
-      <c r="O6" s="21"/>
-      <c r="P6" s="22"/>
-      <c r="Q6" s="23"/>
-      <c r="R6" s="34"/>
-      <c r="S6" s="35"/>
-      <c r="T6" s="36"/>
-      <c r="V6" s="20"/>
-      <c r="W6" s="21"/>
-      <c r="X6" s="22"/>
+      <c r="B6" s="22"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="24"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="23"/>
+      <c r="H6" s="24"/>
+      <c r="J6" s="22"/>
+      <c r="K6" s="23"/>
+      <c r="L6" s="24"/>
+      <c r="N6" s="22"/>
+      <c r="O6" s="23"/>
+      <c r="P6" s="24"/>
+      <c r="R6" s="31"/>
+      <c r="S6" s="32"/>
+      <c r="T6" s="33"/>
+      <c r="V6" s="22"/>
+      <c r="W6" s="23"/>
+      <c r="X6" s="24"/>
     </row>
     <row r="7" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B7" s="20"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="23"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="21"/>
-      <c r="H7" s="22"/>
-      <c r="I7" s="23"/>
-      <c r="J7" s="20"/>
-      <c r="K7" s="21"/>
-      <c r="L7" s="22"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="20"/>
-      <c r="O7" s="21"/>
-      <c r="P7" s="22"/>
-      <c r="Q7" s="23"/>
-      <c r="R7" s="34"/>
-      <c r="S7" s="35"/>
-      <c r="T7" s="36"/>
-      <c r="V7" s="20"/>
-      <c r="W7" s="21"/>
-      <c r="X7" s="22"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="24"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="24"/>
+      <c r="J7" s="22"/>
+      <c r="K7" s="23"/>
+      <c r="L7" s="24"/>
+      <c r="N7" s="22"/>
+      <c r="O7" s="23"/>
+      <c r="P7" s="24"/>
+      <c r="R7" s="31"/>
+      <c r="S7" s="32"/>
+      <c r="T7" s="33"/>
+      <c r="V7" s="22"/>
+      <c r="W7" s="23"/>
+      <c r="X7" s="24"/>
     </row>
     <row r="8" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B8" s="25" t="s">
@@ -4447,30 +4440,26 @@
       </c>
       <c r="C8" s="26"/>
       <c r="D8" s="27"/>
-      <c r="E8" s="23"/>
       <c r="F8" s="25" t="s">
         <v>78</v>
       </c>
       <c r="G8" s="26"/>
       <c r="H8" s="27"/>
-      <c r="I8" s="23"/>
       <c r="J8" s="25" t="s">
         <v>79</v>
       </c>
       <c r="K8" s="26"/>
       <c r="L8" s="27"/>
-      <c r="M8" s="23"/>
       <c r="N8" s="25" t="s">
         <v>80</v>
       </c>
       <c r="O8" s="26"/>
       <c r="P8" s="27"/>
-      <c r="Q8" s="23"/>
-      <c r="R8" s="28" t="s">
+      <c r="R8" s="34" t="s">
         <v>81</v>
       </c>
-      <c r="S8" s="29"/>
-      <c r="T8" s="30"/>
+      <c r="S8" s="35"/>
+      <c r="T8" s="36"/>
       <c r="V8" s="25" t="s">
         <v>82</v>
       </c>
@@ -4478,7 +4467,7 @@
       <c r="X8" s="27"/>
     </row>
     <row r="10" spans="2:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="37" t="s">
+      <c r="B10" s="15" t="s">
         <v>83</v>
       </c>
     </row>
@@ -4486,16 +4475,16 @@
       <c r="B11" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="C11" s="38" t="s">
+      <c r="C11" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="38"/>
+      <c r="D11" s="16"/>
     </row>
     <row r="12" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B12" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="C12" s="24" t="str">
+      <c r="C12" s="14" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C11,Absenteeism!A4:A32,Absenteeism!F4:F32,"Not found")&amp;"%","Enter a name")</f>
         <v>30.8%</v>
       </c>
@@ -4504,7 +4493,7 @@
       <c r="B13" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="C13" s="24">
+      <c r="C13" s="14">
         <f>IFERROR(_xlfn.XLOOKUP(C11,Absenteeism!A4:A32,Absenteeism!D4:D32,"Not found"),"Enter a name")</f>
         <v>18</v>
       </c>
@@ -4513,7 +4502,7 @@
       <c r="B14" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="C14" s="24">
+      <c r="C14" s="14">
         <f>IFERROR(_xlfn.XLOOKUP(C11,'Late Arrivals'!A4:A28, 'Late Arrivals'!B4:B28,0),"No late records")</f>
         <v>7</v>
       </c>
@@ -6286,8 +6275,8 @@
       <c r="B4" s="4">
         <v>397</v>
       </c>
-      <c r="C4" s="4">
-        <v>44.2</v>
+      <c r="C4" s="37">
+        <v>0.442</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -6297,8 +6286,8 @@
       <c r="B5" s="5">
         <v>271</v>
       </c>
-      <c r="C5" s="5">
-        <v>30.1</v>
+      <c r="C5" s="38">
+        <v>0.30099999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -6308,8 +6297,8 @@
       <c r="B6" s="4">
         <v>204</v>
       </c>
-      <c r="C6" s="4">
-        <v>22.7</v>
+      <c r="C6" s="37">
+        <v>0.22700000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -6319,8 +6308,8 @@
       <c r="B7" s="5">
         <v>16</v>
       </c>
-      <c r="C7" s="5">
-        <v>1.8</v>
+      <c r="C7" s="38">
+        <v>1.7999999999999999E-2</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -6330,8 +6319,8 @@
       <c r="B8" s="4">
         <v>10</v>
       </c>
-      <c r="C8" s="4">
-        <v>1.1000000000000001</v>
+      <c r="C8" s="37">
+        <v>1.0999999999999999E-2</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -6341,8 +6330,8 @@
       <c r="B9" s="5">
         <v>1</v>
       </c>
-      <c r="C9" s="5">
-        <v>0.1</v>
+      <c r="C9" s="38">
+        <v>1E-3</v>
       </c>
     </row>
   </sheetData>
@@ -7021,7 +7010,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="11" t="s">
         <v>73</v>
       </c>
       <c r="B1" t="s">
@@ -7029,247 +7018,247 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="15">
+      <c r="B2">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="15">
+      <c r="B3">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5">
         <v>3.8</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6">
         <v>15.4</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7">
         <v>30.8</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8">
         <v>30.8</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="15">
+      <c r="B9">
         <v>46.2</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="15">
+      <c r="B10">
         <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="14" t="s">
+      <c r="A11" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="15">
+      <c r="B11">
         <v>65.400000000000006</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="14" t="s">
+      <c r="A12" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="15">
+      <c r="B12">
         <v>65.400000000000006</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
+      <c r="A13" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="15">
+      <c r="B13">
         <v>65.400000000000006</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="s">
+      <c r="A14" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="15">
+      <c r="B14">
         <v>69.2</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="15">
+      <c r="B15">
         <v>69.2</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="14" t="s">
+      <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="15">
+      <c r="B16">
         <v>73.099999999999994</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B17" s="15">
+      <c r="B17">
         <v>73.099999999999994</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="s">
+      <c r="A18" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="15">
+      <c r="B18">
         <v>73.099999999999994</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B19" s="15">
+      <c r="B19">
         <v>73.099999999999994</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="14" t="s">
+      <c r="A20" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B20" s="15">
+      <c r="B20">
         <v>73.099999999999994</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
+      <c r="A21" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="15">
+      <c r="B21">
         <v>73.099999999999994</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
+      <c r="A22" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B22" s="15">
+      <c r="B22">
         <v>76.900000000000006</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="14" t="s">
+      <c r="A23" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="15">
+      <c r="B23">
         <v>76.900000000000006</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="14" t="s">
+      <c r="A24" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B24" s="15">
+      <c r="B24">
         <v>76.900000000000006</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="14" t="s">
+      <c r="A25" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B25" s="15">
+      <c r="B25">
         <v>76.900000000000006</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="14" t="s">
+      <c r="A26" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="15">
+      <c r="B26">
         <v>80.8</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="14" t="s">
+      <c r="A27" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B27" s="15">
+      <c r="B27">
         <v>80.8</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="14" t="s">
+      <c r="A28" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="B28" s="15">
+      <c r="B28">
         <v>80.8</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="14" t="s">
+      <c r="A29" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B29" s="15">
+      <c r="B29">
         <v>80.8</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="14" t="s">
+      <c r="A30" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="B30" s="15">
+      <c r="B30">
         <v>80.8</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="14" t="s">
+      <c r="A31" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="B31" s="16">
+      <c r="B31" s="13">
         <v>57.303448275862074</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="13" t="s">
+      <c r="A35" s="11" t="s">
         <v>73</v>
       </c>
       <c r="B35" t="s">
@@ -7277,242 +7266,242 @@
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="14" t="s">
+      <c r="A36" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="15">
+      <c r="B36">
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="14" t="s">
+      <c r="A37" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="B37" s="15">
+      <c r="B37">
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="14" t="s">
+      <c r="A38" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="B38" s="15">
+      <c r="B38">
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="14" t="s">
+      <c r="A39" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="B39" s="15">
+      <c r="B39">
         <v>3.8</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="14" t="s">
+      <c r="A40" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="B40" s="15">
+      <c r="B40">
         <v>15.4</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="14" t="s">
+      <c r="A41" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="B41" s="15">
+      <c r="B41">
         <v>30.8</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="14" t="s">
+      <c r="A42" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B42" s="15">
+      <c r="B42">
         <v>30.8</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="14" t="s">
+      <c r="A43" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="B43" s="15">
+      <c r="B43">
         <v>46.2</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="14" t="s">
+      <c r="A44" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="B44" s="15">
+      <c r="B44">
         <v>50</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="14" t="s">
+      <c r="A45" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B45" s="15">
+      <c r="B45">
         <v>65.400000000000006</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="14" t="s">
+      <c r="A46" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B46" s="15">
+      <c r="B46">
         <v>65.400000000000006</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="14" t="s">
+      <c r="A47" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B47" s="15">
+      <c r="B47">
         <v>65.400000000000006</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="14" t="s">
+      <c r="A48" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B48" s="15">
+      <c r="B48">
         <v>69.2</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="14" t="s">
+      <c r="A49" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="B49" s="15">
+      <c r="B49">
         <v>69.2</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="14" t="s">
+      <c r="A50" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="B50" s="15">
+      <c r="B50">
         <v>73.099999999999994</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="14" t="s">
+      <c r="A51" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B51" s="15">
+      <c r="B51">
         <v>73.099999999999994</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="14" t="s">
+      <c r="A52" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="B52" s="15">
+      <c r="B52">
         <v>73.099999999999994</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="14" t="s">
+      <c r="A53" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B53" s="15">
+      <c r="B53">
         <v>73.099999999999994</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="14" t="s">
+      <c r="A54" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B54" s="15">
+      <c r="B54">
         <v>73.099999999999994</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="14" t="s">
+      <c r="A55" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="B55" s="15">
+      <c r="B55">
         <v>73.099999999999994</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="14" t="s">
+      <c r="A56" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B56" s="15">
+      <c r="B56">
         <v>76.900000000000006</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" s="14" t="s">
+      <c r="A57" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="B57" s="15">
+      <c r="B57">
         <v>76.900000000000006</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" s="14" t="s">
+      <c r="A58" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B58" s="15">
+      <c r="B58">
         <v>76.900000000000006</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="14" t="s">
+      <c r="A59" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B59" s="15">
+      <c r="B59">
         <v>76.900000000000006</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" s="14" t="s">
+      <c r="A60" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="B60" s="15">
+      <c r="B60">
         <v>80.8</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" s="14" t="s">
+      <c r="A61" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B61" s="15">
+      <c r="B61">
         <v>80.8</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" s="14" t="s">
+      <c r="A62" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="B62" s="15">
+      <c r="B62">
         <v>80.8</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" s="14" t="s">
+      <c r="A63" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B63" s="15">
+      <c r="B63">
         <v>80.8</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" s="14" t="s">
+      <c r="A64" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="B64" s="15">
+      <c r="B64">
         <v>80.8</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" s="14" t="s">
+      <c r="A65" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="B65" s="15">
+      <c r="B65">
         <v>1661.8000000000002</v>
       </c>
     </row>
